--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_FULL\SuppXLS\Policy_1\Dobre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Downloads\Models MSc_SELECT_updated-20260606\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F785791-9CB0-4EE1-816B-CC1CB2B4ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A555ACBD-529C-4EB1-B1BE-D55843B85681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FLO_SUBSIDY" sheetId="2" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="11">
   <si>
     <t>Year</t>
   </si>
@@ -186,7 +186,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -195,6 +195,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -219,15 +220,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -242,8 +243,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628650" y="1362075"/>
-          <a:ext cx="4743450" cy="714375"/>
+          <a:off x="222250" y="2463800"/>
+          <a:ext cx="6527800" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -722,29 +723,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
@@ -767,7 +768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
         <v>6</v>
       </c>
@@ -784,7 +785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>6</v>
       </c>
@@ -801,7 +802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>6</v>
       </c>
@@ -815,6 +816,132 @@
         <v>9</v>
       </c>
       <c r="H5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>2023</v>
+      </c>
+      <c r="F6">
+        <f>0.07*5*1000</f>
+        <v>350.00000000000006</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="6">
+        <f>0.0803027*5*1000</f>
+        <v>401.51350000000002</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>2030</v>
+      </c>
+      <c r="F8" s="6">
+        <f>0.1023421*5*1000</f>
+        <v>511.71050000000008</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>2035</v>
+      </c>
+      <c r="F9" s="6">
+        <f>0.1484647*5*1000</f>
+        <v>742.32350000000008</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>2040</v>
+      </c>
+      <c r="F10" s="6">
+        <f>0.1984647*5*1000</f>
+        <v>992.32349999999997</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>2045</v>
+      </c>
+      <c r="F11" s="6">
+        <f>0.2484647*5*1000</f>
+        <v>1242.3235000000002</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>2050</v>
+      </c>
+      <c r="F12" s="6">
+        <f>0.2932147*5*1000</f>
+        <v>1466.0735</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -827,26 +954,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c8a3173f591826d139beec1ab1c321b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6c64c9e569b4593220799f669190593" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -1089,32 +1196,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82319D87-9F89-465F-A992-21F87A25DE83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C1AF4FF-0628-4F57-A159-819DC63143E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1131,4 +1233,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82319D87-9F89-465F-A992-21F87A25DE83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Downloads\Models MSc_SELECT_updated-20260606\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A555ACBD-529C-4EB1-B1BE-D55843B85681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E698D2B2-C8A5-48B3-AC40-1E6E77195A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -827,8 +827,8 @@
         <v>2023</v>
       </c>
       <c r="F6">
-        <f>0.07*5*1000</f>
-        <v>350.00000000000006</v>
+        <f>0.07*1000</f>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
         <v>9</v>
@@ -845,8 +845,8 @@
         <v>2025</v>
       </c>
       <c r="F7" s="6">
-        <f>0.0803027*5*1000</f>
-        <v>401.51350000000002</v>
+        <f>0.0803027*2*1000</f>
+        <v>160.6054</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
@@ -863,8 +863,8 @@
         <v>2030</v>
       </c>
       <c r="F8" s="6">
-        <f>0.1023421*5*1000</f>
-        <v>511.71050000000008</v>
+        <f>0.1023421*2*1000</f>
+        <v>204.6842</v>
       </c>
       <c r="G8" t="s">
         <v>9</v>
@@ -881,8 +881,8 @@
         <v>2035</v>
       </c>
       <c r="F9" s="6">
-        <f>0.1484647*5*1000</f>
-        <v>742.32350000000008</v>
+        <f>0.1484647*2*1000</f>
+        <v>296.92939999999999</v>
       </c>
       <c r="G9" t="s">
         <v>9</v>
@@ -899,8 +899,8 @@
         <v>2040</v>
       </c>
       <c r="F10" s="6">
-        <f>0.1984647*5*1000</f>
-        <v>992.32349999999997</v>
+        <f>0.1984647*2*1000</f>
+        <v>396.92939999999999</v>
       </c>
       <c r="G10" t="s">
         <v>9</v>
@@ -917,8 +917,8 @@
         <v>2045</v>
       </c>
       <c r="F11" s="6">
-        <f>0.2484647*5*1000</f>
-        <v>1242.3235000000002</v>
+        <f>0.2484647*2*1000</f>
+        <v>496.92940000000004</v>
       </c>
       <c r="G11" t="s">
         <v>9</v>
@@ -935,8 +935,8 @@
         <v>2050</v>
       </c>
       <c r="F12" s="6">
-        <f>0.2932147*5*1000</f>
-        <v>1466.0735</v>
+        <f>0.2932147*2*1000</f>
+        <v>586.42939999999999</v>
       </c>
       <c r="G12" t="s">
         <v>9</v>
@@ -954,6 +954,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c8a3173f591826d139beec1ab1c321b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6c64c9e569b4593220799f669190593" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -1196,15 +1205,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1217,6 +1217,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C1AF4FF-0628-4F57-A159-819DC63143E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1231,14 +1239,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Downloads\Models MSc_SELECT_updated-20260606\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E698D2B2-C8A5-48B3-AC40-1E6E77195A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A9E0BD-A710-4EE2-BD28-C04446FB399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -845,8 +845,8 @@
         <v>2025</v>
       </c>
       <c r="F7" s="6">
-        <f>0.0803027*2*1000</f>
-        <v>160.6054</v>
+        <f>0.0803027*5*1000</f>
+        <v>401.51350000000002</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
@@ -863,8 +863,8 @@
         <v>2030</v>
       </c>
       <c r="F8" s="6">
-        <f>0.1023421*2*1000</f>
-        <v>204.6842</v>
+        <f>0.1023421*5*1000</f>
+        <v>511.71050000000008</v>
       </c>
       <c r="G8" t="s">
         <v>9</v>
@@ -881,8 +881,8 @@
         <v>2035</v>
       </c>
       <c r="F9" s="6">
-        <f>0.1484647*2*1000</f>
-        <v>296.92939999999999</v>
+        <f>0.1484647*5*1000</f>
+        <v>742.32350000000008</v>
       </c>
       <c r="G9" t="s">
         <v>9</v>
@@ -899,8 +899,8 @@
         <v>2040</v>
       </c>
       <c r="F10" s="6">
-        <f>0.1984647*2*1000</f>
-        <v>396.92939999999999</v>
+        <f>0.1984647*5*1000</f>
+        <v>992.32349999999997</v>
       </c>
       <c r="G10" t="s">
         <v>9</v>
@@ -917,8 +917,8 @@
         <v>2045</v>
       </c>
       <c r="F11" s="6">
-        <f>0.2484647*2*1000</f>
-        <v>496.92940000000004</v>
+        <f>0.2484647*5*1000</f>
+        <v>1242.3235000000002</v>
       </c>
       <c r="G11" t="s">
         <v>9</v>
@@ -935,8 +935,8 @@
         <v>2050</v>
       </c>
       <c r="F12" s="6">
-        <f>0.2932147*2*1000</f>
-        <v>586.42939999999999</v>
+        <f>0.2932147*5*1000</f>
+        <v>1466.0735</v>
       </c>
       <c r="G12" t="s">
         <v>9</v>
@@ -954,15 +954,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c8a3173f591826d139beec1ab1c321b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6c64c9e569b4593220799f669190593" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -1205,6 +1196,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1217,14 +1217,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C1AF4FF-0628-4F57-A159-819DC63143E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1239,6 +1231,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
